--- a/data/crops/rothc_support/tomatoes_rothc_scenarios_2.xlsx
+++ b/data/crops/rothc_support/tomatoes_rothc_scenarios_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldwildlifefund-my.sharepoint.com/personal/cristobal_loyola_wwfus_org/Documents/Documents/203. Python projects/SBTN_Test/data/crops/rothc_support/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70EEC35A-A2A3-40C9-909C-220BF46F3F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{70EEC35A-A2A3-40C9-909C-220BF46F3F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E663E1A-82ED-4900-80D3-540A99A7239F}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6F94B64D-243B-49DA-AE87-045B34BFAB0F}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="19200" windowHeight="11180" xr2:uid="{6F94B64D-243B-49DA-AE87-045B34BFAB0F}"/>
   </bookViews>
   <sheets>
     <sheet name="scenarios" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2287" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2298" uniqueCount="620">
   <si>
     <t>crop_name</t>
   </si>
@@ -1934,12 +1934,6 @@
     <t>apply_local_zscore</t>
   </si>
   <si>
-    <t>ratio_percentile</t>
-  </si>
-  <si>
-    <t>sd</t>
-  </si>
-  <si>
     <t>../LEAFs/SOC/rasters/test</t>
   </si>
   <si>
@@ -1958,14 +1952,26 @@
     <t>yield_global_percentile_cap</t>
   </si>
   <si>
-    <t>fao_max_ratio</t>
+    <t>result_basename</t>
+  </si>
+  <si>
+    <t>Tomato_irr_2030y_log_winsor_0199_gym_99.tif</t>
+  </si>
+  <si>
+    <t>Tomato_irr_2030y_log_winsor_0199_gym_99_gsocm_99.tif</t>
+  </si>
+  <si>
+    <t>Tomato_irr_2030y_log_winsor_0199_gsocm_99.tif</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2011,6 +2017,11 @@
       <color rgb="FFFF7EDB"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2072,7 +2083,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2088,6 +2099,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2526,7 +2538,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1821CC5-2977-4A1A-B60B-8C004F05C4AF}">
   <dimension ref="A1:AF7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.1796875" bestFit="1" customWidth="1"/>
@@ -2535,9 +2547,11 @@
     <col min="6" max="6" width="18.26953125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.81640625" customWidth="1"/>
     <col min="8" max="8" width="63.6328125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="20.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2617,25 +2631,25 @@
         <v>608</v>
       </c>
       <c r="AA1" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="AB1" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="AC1" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="AD1" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="AC1" s="10" t="s">
+      <c r="AE1" s="10" t="s">
         <v>614</v>
       </c>
-      <c r="AD1" s="10" t="s">
+      <c r="AF1" s="11" t="s">
         <v>615</v>
       </c>
-      <c r="AE1" s="10" t="s">
-        <v>616</v>
-      </c>
-      <c r="AF1" s="10" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -2652,7 +2666,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G2" t="str">
         <f t="shared" ref="G2" si="0">+"RothC results for year 2030 for "&amp;A2&amp;"_"&amp;D2&amp;" in ton C/ha"</f>
@@ -2716,11 +2730,20 @@
       <c r="AB2">
         <v>99</v>
       </c>
-      <c r="AE2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AC2" t="s">
+        <v>619</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>619</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>619</v>
+      </c>
+      <c r="AF2" s="9" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -2737,10 +2760,10 @@
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G3" t="str">
-        <f t="shared" ref="G3:G4" si="2">+"RothC results for year 2030 for "&amp;A3&amp;"_"&amp;D3&amp;" in ton C/ha"</f>
+        <f t="shared" ref="G3" si="2">+"RothC results for year 2030 for "&amp;A3&amp;"_"&amp;D3&amp;" in ton C/ha"</f>
         <v>RothC results for year 2030 for Tomato_irr in ton C/ha</v>
       </c>
       <c r="H3" s="5" t="s">
@@ -2765,7 +2788,7 @@
         <v>100</v>
       </c>
       <c r="Q3" t="str">
-        <f t="shared" ref="Q3:Q4" si="3">+S3</f>
+        <f t="shared" ref="Q3" si="3">+S3</f>
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.TOM.WSI.tif</v>
       </c>
       <c r="R3" s="5" t="s">
@@ -2783,8 +2806,8 @@
       <c r="V3" s="7" t="s">
         <v>597</v>
       </c>
-      <c r="W3" s="9" t="s">
-        <v>609</v>
+      <c r="W3" t="s">
+        <v>601</v>
       </c>
       <c r="X3" t="s">
         <v>602</v>
@@ -2801,11 +2824,20 @@
       <c r="AB3">
         <v>99</v>
       </c>
+      <c r="AC3" t="s">
+        <v>619</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>619</v>
+      </c>
       <c r="AE3">
         <v>99</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AF3" s="9" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -2822,10 +2854,10 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="G4" si="4">+"RothC results for year 2030 for "&amp;A4&amp;"_"&amp;D4&amp;" in ton C/ha"</f>
         <v>RothC results for year 2030 for Tomato_irr in ton C/ha</v>
       </c>
       <c r="H4" s="5" t="s">
@@ -2850,7 +2882,7 @@
         <v>100</v>
       </c>
       <c r="Q4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="Q4" si="5">+S4</f>
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.TOM.WSI.tif</v>
       </c>
       <c r="R4" s="5" t="s">
@@ -2868,29 +2900,38 @@
       <c r="V4" s="7" t="s">
         <v>597</v>
       </c>
-      <c r="W4" s="9" t="s">
-        <v>610</v>
+      <c r="W4" t="s">
+        <v>601</v>
       </c>
       <c r="X4" t="s">
         <v>602</v>
       </c>
       <c r="Y4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="b">
         <v>1</v>
       </c>
       <c r="AA4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB4">
-        <v>99</v>
+        <v>0</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>619</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>619</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>619</v>
       </c>
       <c r="AE4">
         <v>99</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AF4" s="9" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32">
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="4"/>
@@ -2898,8 +2939,9 @@
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="6"/>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="AF5" s="9"/>
+    </row>
+    <row r="6" spans="1:32">
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="4"/>
@@ -2909,7 +2951,7 @@
       <c r="T6" s="6"/>
       <c r="W6" s="9"/>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32">
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="4"/>
@@ -2929,7 +2971,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A7C158A-EE11-489A-9157-EB898838B392}">
   <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
@@ -2938,7 +2980,7 @@
     <col min="5" max="7" width="80.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2961,7 +3003,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -2984,7 +3026,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -3007,7 +3049,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -3030,7 +3072,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -3053,7 +3095,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -3076,7 +3118,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -3099,7 +3141,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -3122,7 +3164,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -3145,7 +3187,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -3168,7 +3210,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -3191,7 +3233,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -3214,7 +3256,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -3237,7 +3279,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -3260,7 +3302,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -3283,7 +3325,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -3306,7 +3348,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -3329,7 +3371,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" hidden="1">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -3352,7 +3394,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" hidden="1">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -3375,7 +3417,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" hidden="1">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -3398,7 +3440,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" hidden="1">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -3421,7 +3463,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" hidden="1">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -3444,7 +3486,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" hidden="1">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -3467,7 +3509,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" hidden="1">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -3490,7 +3532,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" hidden="1">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -3513,7 +3555,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" hidden="1">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -3536,7 +3578,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" hidden="1">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -3559,7 +3601,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" hidden="1">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -3582,7 +3624,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -3605,7 +3647,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" hidden="1">
       <c r="A30" t="s">
         <v>19</v>
       </c>
@@ -3628,7 +3670,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -3651,7 +3693,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -3674,7 +3716,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -3697,7 +3739,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -3720,7 +3762,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -3754,13 +3796,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B028805-B7C7-4EC7-B194-4DB0911705EB}">
   <dimension ref="A1:D38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="28.08984375" customWidth="1"/>
     <col min="2" max="4" width="80.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3774,7 +3816,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>465</v>
       </c>
@@ -3788,7 +3830,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -3802,7 +3844,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>472</v>
       </c>
@@ -3816,7 +3858,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -3830,7 +3872,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>63</v>
       </c>
@@ -3844,7 +3886,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>60</v>
       </c>
@@ -3858,7 +3900,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>485</v>
       </c>
@@ -3872,7 +3914,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>140</v>
       </c>
@@ -3886,7 +3928,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>492</v>
       </c>
@@ -3900,7 +3942,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>496</v>
       </c>
@@ -3914,7 +3956,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>500</v>
       </c>
@@ -3928,7 +3970,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>504</v>
       </c>
@@ -3942,7 +3984,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>508</v>
       </c>
@@ -3956,7 +3998,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -3970,7 +4012,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>515</v>
       </c>
@@ -3984,7 +4026,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>519</v>
       </c>
@@ -3998,7 +4040,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>523</v>
       </c>
@@ -4012,7 +4054,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>76</v>
       </c>
@@ -4026,7 +4068,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>530</v>
       </c>
@@ -4040,7 +4082,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>534</v>
       </c>
@@ -4054,7 +4096,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>538</v>
       </c>
@@ -4068,7 +4110,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>542</v>
       </c>
@@ -4082,7 +4124,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>546</v>
       </c>
@@ -4096,7 +4138,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -4110,7 +4152,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -4124,7 +4166,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>556</v>
       </c>
@@ -4138,7 +4180,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>560</v>
       </c>
@@ -4152,7 +4194,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>564</v>
       </c>
@@ -4166,7 +4208,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>102</v>
       </c>
@@ -4180,7 +4222,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -4194,7 +4236,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -4208,7 +4250,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
         <v>27</v>
       </c>
@@ -4222,7 +4264,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -4236,7 +4278,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
         <v>583</v>
       </c>
@@ -4250,7 +4292,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
         <v>587</v>
       </c>
@@ -4264,7 +4306,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
         <v>32</v>
       </c>
@@ -4278,7 +4320,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
         <v>33</v>
       </c>
@@ -4303,7 +4345,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{911D9E33-3F34-49B5-848C-E1F20B597264}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4312,13 +4354,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7192511D-CF8D-4308-B7D5-BC33E58873EC}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -4335,7 +4377,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -4352,7 +4394,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>47</v>
       </c>
@@ -4369,7 +4411,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -4386,7 +4428,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -4403,7 +4445,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -4420,7 +4462,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -4437,7 +4479,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>60</v>
       </c>
@@ -4454,7 +4496,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>63</v>
       </c>
@@ -4471,7 +4513,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -4488,7 +4530,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>69</v>
       </c>
@@ -4505,7 +4547,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -4522,7 +4564,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -4539,7 +4581,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>75</v>
       </c>
@@ -4556,7 +4598,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>79</v>
       </c>
@@ -4573,7 +4615,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -4590,7 +4632,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>83</v>
       </c>
@@ -4607,7 +4649,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -4624,7 +4666,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -4641,7 +4683,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -4658,7 +4700,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -4675,7 +4717,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -4692,7 +4734,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -4709,7 +4751,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -4726,7 +4768,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -4743,7 +4785,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -4760,7 +4802,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -4777,7 +4819,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -4794,7 +4836,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -4819,12 +4861,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A673E04-3101-4A6E-90E1-42862EC2370A}">
   <dimension ref="A1:AB139"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="33.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28">
       <c r="A1" t="s">
         <v>113</v>
       </c>
@@ -4898,7 +4940,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28">
       <c r="A2" t="s">
         <v>118</v>
       </c>
@@ -4972,7 +5014,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28">
       <c r="A3" t="s">
         <v>123</v>
       </c>
@@ -5046,7 +5088,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28">
       <c r="A4" t="s">
         <v>126</v>
       </c>
@@ -5120,7 +5162,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28">
       <c r="A5" t="s">
         <v>129</v>
       </c>
@@ -5194,7 +5236,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28">
       <c r="A6" t="s">
         <v>131</v>
       </c>
@@ -5268,7 +5310,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28">
       <c r="A7" t="s">
         <v>132</v>
       </c>
@@ -5342,7 +5384,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28">
       <c r="A8" t="s">
         <v>133</v>
       </c>
@@ -5416,7 +5458,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:28">
       <c r="A9" t="s">
         <v>136</v>
       </c>
@@ -5490,7 +5532,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:28">
       <c r="A10" t="s">
         <v>137</v>
       </c>
@@ -5564,7 +5606,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:28">
       <c r="A11" t="s">
         <v>138</v>
       </c>
@@ -5638,7 +5680,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:28">
       <c r="A12" t="s">
         <v>141</v>
       </c>
@@ -5712,7 +5754,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:28">
       <c r="A13" t="s">
         <v>142</v>
       </c>
@@ -5786,7 +5828,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:28">
       <c r="A14" t="s">
         <v>143</v>
       </c>
@@ -5860,7 +5902,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:28">
       <c r="A15" t="s">
         <v>146</v>
       </c>
@@ -5934,7 +5976,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:28">
       <c r="A16" t="s">
         <v>147</v>
       </c>
@@ -6008,7 +6050,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:28">
       <c r="A17" t="s">
         <v>148</v>
       </c>
@@ -6082,7 +6124,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:28">
       <c r="A18" t="s">
         <v>150</v>
       </c>
@@ -6156,7 +6198,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:28">
       <c r="A19" t="s">
         <v>151</v>
       </c>
@@ -6230,7 +6272,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:28">
       <c r="A20" t="s">
         <v>152</v>
       </c>
@@ -6304,7 +6346,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:28">
       <c r="A21" t="s">
         <v>154</v>
       </c>
@@ -6378,7 +6420,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:28">
       <c r="A22" t="s">
         <v>155</v>
       </c>
@@ -6452,7 +6494,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:28">
       <c r="A23" t="s">
         <v>156</v>
       </c>
@@ -6526,7 +6568,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:28">
       <c r="A24" t="s">
         <v>158</v>
       </c>
@@ -6600,7 +6642,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:28">
       <c r="A25" t="s">
         <v>159</v>
       </c>
@@ -6674,7 +6716,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:28">
       <c r="A26" t="s">
         <v>160</v>
       </c>
@@ -6748,7 +6790,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:28">
       <c r="A27" t="s">
         <v>162</v>
       </c>
@@ -6822,7 +6864,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:28">
       <c r="A28" t="s">
         <v>163</v>
       </c>
@@ -6896,7 +6938,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:28">
       <c r="A29" t="s">
         <v>164</v>
       </c>
@@ -6970,7 +7012,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:28">
       <c r="A30" t="s">
         <v>166</v>
       </c>
@@ -7044,7 +7086,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:28">
       <c r="A31" t="s">
         <v>167</v>
       </c>
@@ -7118,7 +7160,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:28">
       <c r="A32" t="s">
         <v>168</v>
       </c>
@@ -7192,7 +7234,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:28">
       <c r="A33" t="s">
         <v>171</v>
       </c>
@@ -7266,7 +7308,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:28">
       <c r="A34" t="s">
         <v>172</v>
       </c>
@@ -7340,7 +7382,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:28">
       <c r="A35" t="s">
         <v>173</v>
       </c>
@@ -7414,7 +7456,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:28">
       <c r="A36" t="s">
         <v>175</v>
       </c>
@@ -7488,7 +7530,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:28">
       <c r="A37" t="s">
         <v>176</v>
       </c>
@@ -7562,7 +7604,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:28">
       <c r="A38" t="s">
         <v>177</v>
       </c>
@@ -7636,7 +7678,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:28">
       <c r="A39" t="s">
         <v>180</v>
       </c>
@@ -7710,7 +7752,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:28">
       <c r="A40" t="s">
         <v>181</v>
       </c>
@@ -7784,7 +7826,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:28">
       <c r="A41" t="s">
         <v>182</v>
       </c>
@@ -7858,7 +7900,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:28">
       <c r="A42" t="s">
         <v>184</v>
       </c>
@@ -7932,7 +7974,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:28">
       <c r="A43" t="s">
         <v>185</v>
       </c>
@@ -8006,7 +8048,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:28">
       <c r="A44" t="s">
         <v>186</v>
       </c>
@@ -8080,7 +8122,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:28">
       <c r="A45" t="s">
         <v>189</v>
       </c>
@@ -8154,7 +8196,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:28">
       <c r="A46" t="s">
         <v>190</v>
       </c>
@@ -8228,7 +8270,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:28">
       <c r="A47" t="s">
         <v>191</v>
       </c>
@@ -8266,7 +8308,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:28">
       <c r="A48" t="s">
         <v>194</v>
       </c>
@@ -8286,7 +8328,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>195</v>
       </c>
@@ -8306,7 +8348,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>196</v>
       </c>
@@ -8326,7 +8368,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>199</v>
       </c>
@@ -8346,7 +8388,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>200</v>
       </c>
@@ -8366,7 +8408,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>201</v>
       </c>
@@ -8386,7 +8428,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>203</v>
       </c>
@@ -8406,7 +8448,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>204</v>
       </c>
@@ -8426,7 +8468,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>205</v>
       </c>
@@ -8446,7 +8488,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>207</v>
       </c>
@@ -8466,7 +8508,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>208</v>
       </c>
@@ -8486,7 +8528,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>209</v>
       </c>
@@ -8506,7 +8548,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>212</v>
       </c>
@@ -8526,7 +8568,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>213</v>
       </c>
@@ -8546,7 +8588,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>214</v>
       </c>
@@ -8566,7 +8608,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>217</v>
       </c>
@@ -8586,7 +8628,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>218</v>
       </c>
@@ -8606,7 +8648,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>219</v>
       </c>
@@ -8626,7 +8668,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>221</v>
       </c>
@@ -8646,7 +8688,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>222</v>
       </c>
@@ -8666,7 +8708,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>223</v>
       </c>
@@ -8686,7 +8728,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>226</v>
       </c>
@@ -8706,7 +8748,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>227</v>
       </c>
@@ -8726,7 +8768,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>228</v>
       </c>
@@ -8746,7 +8788,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>231</v>
       </c>
@@ -8766,7 +8808,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>232</v>
       </c>
@@ -8786,7 +8828,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>233</v>
       </c>
@@ -8806,7 +8848,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>236</v>
       </c>
@@ -8826,7 +8868,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>237</v>
       </c>
@@ -8846,7 +8888,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>238</v>
       </c>
@@ -8866,7 +8908,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>240</v>
       </c>
@@ -8886,7 +8928,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>241</v>
       </c>
@@ -8906,7 +8948,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>242</v>
       </c>
@@ -8926,7 +8968,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>244</v>
       </c>
@@ -8946,7 +8988,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>245</v>
       </c>
@@ -8966,7 +9008,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>246</v>
       </c>
@@ -8986,7 +9028,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>249</v>
       </c>
@@ -9006,7 +9048,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>250</v>
       </c>
@@ -9026,7 +9068,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>251</v>
       </c>
@@ -9046,7 +9088,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>254</v>
       </c>
@@ -9066,7 +9108,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>255</v>
       </c>
@@ -9086,7 +9128,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>256</v>
       </c>
@@ -9106,7 +9148,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>258</v>
       </c>
@@ -9126,7 +9168,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>259</v>
       </c>
@@ -9146,7 +9188,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>260</v>
       </c>
@@ -9166,7 +9208,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>263</v>
       </c>
@@ -9186,7 +9228,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>264</v>
       </c>
@@ -9206,7 +9248,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>265</v>
       </c>
@@ -9226,7 +9268,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>268</v>
       </c>
@@ -9246,7 +9288,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>269</v>
       </c>
@@ -9266,7 +9308,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>270</v>
       </c>
@@ -9286,7 +9328,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>272</v>
       </c>
@@ -9306,7 +9348,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>273</v>
       </c>
@@ -9326,7 +9368,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>274</v>
       </c>
@@ -9346,7 +9388,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>276</v>
       </c>
@@ -9366,7 +9408,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>277</v>
       </c>
@@ -9386,7 +9428,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>278</v>
       </c>
@@ -9406,7 +9448,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>280</v>
       </c>
@@ -9426,7 +9468,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>281</v>
       </c>
@@ -9446,7 +9488,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>282</v>
       </c>
@@ -9466,7 +9508,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
         <v>284</v>
       </c>
@@ -9486,7 +9528,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
         <v>285</v>
       </c>
@@ -9506,7 +9548,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>286</v>
       </c>
@@ -9526,7 +9568,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>288</v>
       </c>
@@ -9546,7 +9588,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>289</v>
       </c>
@@ -9566,7 +9608,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>290</v>
       </c>
@@ -9586,7 +9628,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>292</v>
       </c>
@@ -9606,7 +9648,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>293</v>
       </c>
@@ -9626,7 +9668,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>294</v>
       </c>
@@ -9646,7 +9688,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>297</v>
       </c>
@@ -9666,7 +9708,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>298</v>
       </c>
@@ -9686,7 +9728,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>299</v>
       </c>
@@ -9706,7 +9748,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>301</v>
       </c>
@@ -9726,7 +9768,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>302</v>
       </c>
@@ -9746,7 +9788,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>303</v>
       </c>
@@ -9766,7 +9808,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>305</v>
       </c>
@@ -9786,7 +9828,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>306</v>
       </c>
@@ -9806,7 +9848,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>307</v>
       </c>
@@ -9826,7 +9868,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>309</v>
       </c>
@@ -9846,7 +9888,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>310</v>
       </c>
@@ -9866,7 +9908,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>311</v>
       </c>
@@ -9886,7 +9928,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
         <v>314</v>
       </c>
@@ -9906,7 +9948,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
         <v>315</v>
       </c>
@@ -9926,7 +9968,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
         <v>316</v>
       </c>
@@ -9946,7 +9988,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
         <v>318</v>
       </c>
@@ -9966,7 +10008,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
         <v>319</v>
       </c>
@@ -9986,7 +10028,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6">
       <c r="A134" t="s">
         <v>320</v>
       </c>
@@ -10006,7 +10048,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6">
       <c r="A135" t="s">
         <v>322</v>
       </c>
@@ -10026,7 +10068,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6">
       <c r="A136" t="s">
         <v>323</v>
       </c>
@@ -10046,7 +10088,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6">
       <c r="A137" t="s">
         <v>324</v>
       </c>
@@ -10066,7 +10108,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
         <v>327</v>
       </c>
@@ -10086,7 +10128,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
         <v>328</v>
       </c>

--- a/data/crops/rothc_support/tomatoes_rothc_scenarios_2.xlsx
+++ b/data/crops/rothc_support/tomatoes_rothc_scenarios_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldwildlifefund-my.sharepoint.com/personal/cristobal_loyola_wwfus_org/Documents/Documents/203. Python projects/SBTN_Test/data/crops/rothc_support/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{70EEC35A-A2A3-40C9-909C-220BF46F3F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E663E1A-82ED-4900-80D3-540A99A7239F}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{70EEC35A-A2A3-40C9-909C-220BF46F3F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{972ABF13-523C-411D-96E2-DD5DAA5D4ED2}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="19200" windowHeight="11180" xr2:uid="{6F94B64D-243B-49DA-AE87-045B34BFAB0F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6F94B64D-243B-49DA-AE87-045B34BFAB0F}"/>
   </bookViews>
   <sheets>
     <sheet name="scenarios" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2298" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2336" uniqueCount="622">
   <si>
     <t>crop_name</t>
   </si>
@@ -1965,6 +1965,12 @@
   </si>
   <si>
     <t>None</t>
+  </si>
+  <si>
+    <t>Tomato_irr_2030y_log_winsor_0199_gsocm_99-99.tif</t>
+  </si>
+  <si>
+    <t>Tomato_irr_2030y_log_winsor_0199_gsocm_99-95.tif</t>
   </si>
 </sst>
 </file>
@@ -2857,7 +2863,7 @@
         <v>609</v>
       </c>
       <c r="G4" t="str">
-        <f t="shared" ref="G4" si="4">+"RothC results for year 2030 for "&amp;A4&amp;"_"&amp;D4&amp;" in ton C/ha"</f>
+        <f t="shared" ref="G4:G5" si="4">+"RothC results for year 2030 for "&amp;A4&amp;"_"&amp;D4&amp;" in ton C/ha"</f>
         <v>RothC results for year 2030 for Tomato_irr in ton C/ha</v>
       </c>
       <c r="H4" s="5" t="s">
@@ -2882,7 +2888,7 @@
         <v>100</v>
       </c>
       <c r="Q4" t="str">
-        <f t="shared" ref="Q4" si="5">+S4</f>
+        <f t="shared" ref="Q4:Q5" si="5">+S4</f>
         <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.TOM.WSI.tif</v>
       </c>
       <c r="R4" s="5" t="s">
@@ -2932,24 +2938,192 @@
       </c>
     </row>
     <row r="5" spans="1:32">
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="4"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="6"/>
-      <c r="AF5" s="9"/>
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>609</v>
+      </c>
+      <c r="G5" t="str">
+        <f t="shared" si="4"/>
+        <v>RothC results for year 2030 for Tomato_irr in ton C/ha</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>100</v>
+      </c>
+      <c r="Q5" t="str">
+        <f t="shared" si="5"/>
+        <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.TOM.WSI.tif</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="T5" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="W5" t="s">
+        <v>601</v>
+      </c>
+      <c r="X5" t="s">
+        <v>602</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>99.5</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>619</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>619</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>619</v>
+      </c>
+      <c r="AF5" s="9" t="s">
+        <v>621</v>
+      </c>
     </row>
     <row r="6" spans="1:32">
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="4"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="6"/>
-      <c r="W6" s="9"/>
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>609</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" ref="G6" si="6">+"RothC results for year 2030 for "&amp;A6&amp;"_"&amp;D6&amp;" in ton C/ha"</f>
+        <v>RothC results for year 2030 for Tomato_irr in ton C/ha</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>100</v>
+      </c>
+      <c r="Q6" t="str">
+        <f t="shared" ref="Q6" si="7">+S6</f>
+        <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.TOM.WSI.tif</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="S6" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="T6" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="W6" t="s">
+        <v>601</v>
+      </c>
+      <c r="X6" t="s">
+        <v>602</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>99.9</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>619</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>619</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>619</v>
+      </c>
+      <c r="AF6" s="9" t="s">
+        <v>620</v>
+      </c>
     </row>
     <row r="7" spans="1:32">
       <c r="H7" s="3"/>

--- a/data/crops/rothc_support/tomatoes_rothc_scenarios_2.xlsx
+++ b/data/crops/rothc_support/tomatoes_rothc_scenarios_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldwildlifefund-my.sharepoint.com/personal/cristobal_loyola_wwfus_org/Documents/Documents/203. Python projects/SBTN_Test/data/crops/rothc_support/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="8_{70EEC35A-A2A3-40C9-909C-220BF46F3F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{972ABF13-523C-411D-96E2-DD5DAA5D4ED2}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{70EEC35A-A2A3-40C9-909C-220BF46F3F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCC727F6-7DF4-4C17-A13A-F4052A012DBB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6F94B64D-243B-49DA-AE87-045B34BFAB0F}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2336" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2322" uniqueCount="621">
   <si>
     <t>crop_name</t>
   </si>
@@ -1962,9 +1962,6 @@
   </si>
   <si>
     <t>Tomato_irr_2030y_log_winsor_0199_gsocm_99.tif</t>
-  </si>
-  <si>
-    <t>None</t>
   </si>
   <si>
     <t>Tomato_irr_2030y_log_winsor_0199_gsocm_99-99.tif</t>
@@ -2736,15 +2733,6 @@
       <c r="AB2">
         <v>99</v>
       </c>
-      <c r="AC2" t="s">
-        <v>619</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>619</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>619</v>
-      </c>
       <c r="AF2" s="9" t="s">
         <v>618</v>
       </c>
@@ -2830,12 +2818,6 @@
       <c r="AB3">
         <v>99</v>
       </c>
-      <c r="AC3" t="s">
-        <v>619</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>619</v>
-      </c>
       <c r="AE3">
         <v>99</v>
       </c>
@@ -2921,15 +2903,6 @@
       <c r="AA4" t="b">
         <v>0</v>
       </c>
-      <c r="AB4" t="s">
-        <v>619</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>619</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>619</v>
-      </c>
       <c r="AE4">
         <v>99</v>
       </c>
@@ -3018,17 +2991,8 @@
       <c r="AB5">
         <v>99.5</v>
       </c>
-      <c r="AC5" t="s">
-        <v>619</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>619</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>619</v>
-      </c>
       <c r="AF5" s="9" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -3112,17 +3076,8 @@
       <c r="AB6">
         <v>99.9</v>
       </c>
-      <c r="AC6" t="s">
+      <c r="AF6" s="9" t="s">
         <v>619</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>619</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>619</v>
-      </c>
-      <c r="AF6" s="9" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="7" spans="1:32">
